--- a/report_templates/Cattle-Deaths-Template.xlsx
+++ b/report_templates/Cattle-Deaths-Template.xlsx
@@ -1,21 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
+  <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3E2F9A2-E688-4FF7-864B-9220AFD20634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="BCMS Stats" sheetId="1" r:id="rId4"/>
+    <sheet name="BCMS Stats" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
@@ -60,7 +80,7 @@
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
@@ -96,6 +116,9 @@
     <t>This report must only be used for the purposes it was requested. It must not be distributed onto any other person(s) or organisation(s) without approval from the BCMS Management Information Team.</t>
   </si>
   <si>
+    <t>Year</t>
+  </si>
+  <si>
     <t>Month Name</t>
   </si>
   <si>
@@ -126,28 +149,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Arial"/>
@@ -158,7 +168,7 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="18"/>
       <color indexed="9"/>
       <name val="Arial"/>
@@ -169,19 +179,19 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
       <color indexed="12"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
       <color indexed="9"/>
       <name val="Arial"/>
@@ -207,7 +217,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -329,15 +339,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -364,79 +365,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -498,141 +426,203 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+  <cellXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -642,58 +632,124 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ff666699"/>
-      <rgbColor rgb="ffff0000"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>340995</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1341120</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1200150</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>726440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 6" descr="Picture 6"/>
+        <xdr:cNvPr id="3" name="Picture 1026" descr="Picture 1026">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="152400" y="0"/>
-          <a:ext cx="1341120" cy="1104900"/>
+          <a:off x="13458825" y="340995"/>
+          <a:ext cx="2762250" cy="385445"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -707,38 +763,45 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>350520</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1828800</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>735965</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>569595</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1026" descr="Picture 1026"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48D052F7-B48E-4EF8-B34E-205FB8306B0D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10096500" y="350520"/>
-          <a:ext cx="3009900" cy="385446"/>
+          <a:off x="133350" y="0"/>
+          <a:ext cx="1341120" cy="1104900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -756,7 +819,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
     <a:clrScheme name="Office Theme 2007 - 2010">
       <a:dk1>
@@ -882,7 +945,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+            <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -891,7 +954,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+            <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -900,7 +963,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw blurRad="38100" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -974,7 +1037,7 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+          <a:outerShdw blurRad="38100" dist="23000" dir="5400000" rotWithShape="0">
             <a:srgbClr val="000000">
               <a:alpha val="35000"/>
             </a:srgbClr>
@@ -982,7 +1045,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1000,7 +1063,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1029,7 +1092,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1054,7 +1117,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1079,7 +1142,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1104,7 +1167,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1129,7 +1192,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1154,7 +1217,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1179,7 +1242,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1204,7 +1267,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1229,7 +1292,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1242,9 +1305,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1259,7 +1328,7 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw blurRad="38100" dist="20000" dir="5400000" rotWithShape="0">
             <a:srgbClr val="000000">
               <a:alpha val="38000"/>
             </a:srgbClr>
@@ -1267,7 +1336,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1285,7 +1354,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1310,7 +1379,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1335,7 +1404,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1360,7 +1429,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1385,7 +1454,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1410,7 +1479,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1435,7 +1504,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1460,7 +1529,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1485,7 +1554,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1510,7 +1579,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1523,9 +1592,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1539,7 +1614,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1557,7 +1632,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1586,7 +1661,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1611,7 +1686,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1636,7 +1711,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1661,7 +1736,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1686,7 +1761,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1711,7 +1786,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1736,7 +1811,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1761,7 +1836,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1786,7 +1861,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1799,255 +1874,279 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="28.1719" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="2.41406" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="12.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="2.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="12.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="87" customHeight="1">
+    <row r="1" spans="1:12" ht="87" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
-      <c r="D1" t="s" s="4">
+      <c r="D1" s="3"/>
+      <c r="E1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="3"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="6"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="5"/>
     </row>
-    <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="12"/>
+    <row r="2" spans="1:12" ht="8.1" customHeight="1">
+      <c r="A2" s="6"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="11"/>
     </row>
-    <row r="3" ht="50.25" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" t="s" s="14">
+    <row r="3" spans="1:12" ht="50.25" customHeight="1">
+      <c r="A3" s="12"/>
+      <c r="B3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="19"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="13"/>
     </row>
-    <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="19"/>
+    <row r="4" spans="1:12" ht="12.75" customHeight="1">
+      <c r="A4" s="6"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="13"/>
     </row>
-    <row r="5" ht="17.4" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" t="s" s="21">
+    <row r="5" spans="1:12" ht="17.45" customHeight="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="22"/>
-      <c r="F5" t="s" s="21">
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="19"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="13"/>
     </row>
-    <row r="6" ht="17.4" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" t="s" s="21">
+    <row r="6" spans="1:12" ht="17.45" customHeight="1">
+      <c r="A6" s="6"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s" s="21">
+      <c r="D6" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="22"/>
-      <c r="F6" t="s" s="21">
+      <c r="E6" s="10"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G6" t="s" s="24">
+      <c r="H6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="19"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="13"/>
     </row>
-    <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="19"/>
+    <row r="7" spans="1:12" ht="12.75" customHeight="1">
+      <c r="A7" s="6"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="13"/>
     </row>
-    <row r="8" ht="27.75" customHeight="1">
-      <c r="A8" s="28"/>
-      <c r="B8" t="s" s="29">
+    <row r="8" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A8" s="6"/>
+      <c r="B8" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="19"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="13"/>
     </row>
-    <row r="9" ht="32.25" customHeight="1">
-      <c r="A9" s="28"/>
-      <c r="B9" t="s" s="33">
+    <row r="9" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="13"/>
     </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="19"/>
+    <row r="10" spans="1:12" ht="12.75" customHeight="1">
+      <c r="A10" s="6"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="13"/>
     </row>
-    <row r="11" ht="15.6" customHeight="1">
-      <c r="A11" s="28"/>
-      <c r="B11" t="s" s="37">
+    <row r="11" spans="1:12" ht="15.6" customHeight="1">
+      <c r="A11" s="19"/>
+      <c r="B11" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C11" t="s" s="37">
+      <c r="C11" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D11" t="s" s="37">
+      <c r="D11" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="E11" t="s" s="37">
+      <c r="E11" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="F11" t="s" s="37">
+      <c r="F11" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G11" t="s" s="37">
+      <c r="G11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="H11" t="s" s="37">
+      <c r="H11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="I11" t="s" s="37">
+      <c r="I11" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J11" t="s" s="37">
+      <c r="J11" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="38"/>
+      <c r="K11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L11" s="22"/>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="28"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="38"/>
+    <row r="12" spans="1:12" ht="15" customHeight="1">
+      <c r="A12" s="19"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="22"/>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="40"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="42"/>
+    <row r="13" spans="1:12" ht="15" customHeight="1">
+      <c r="A13" s="24"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="B9:K9"/>
   </mergeCells>
-  <pageMargins left="0.19685" right="0.19685" top="0.393701" bottom="0.393701" header="0.511811" footer="0.511811"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageMargins left="0.19685" right="0.19685" top="0.39370100000000002" bottom="0.39370100000000002" header="0.51181100000000002" footer="0.51181100000000002"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/report_templates/Cattle-Deaths-Template.xlsx
+++ b/report_templates/Cattle-Deaths-Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3E2F9A2-E688-4FF7-864B-9220AFD20634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49961780-C035-4DCE-808B-EA99602BA349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -137,10 +137,10 @@
     <t>Country</t>
   </si>
   <si>
-    <t>Age at Death in Months</t>
+    <t>County</t>
   </si>
   <si>
-    <t>Premise Type Groups</t>
+    <t>Age at Death in Months</t>
   </si>
   <si>
     <t>Number of Deaths</t>
@@ -510,101 +510,101 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1920,117 +1920,117 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
+      <c r="J1" s="26"/>
       <c r="K1" s="3"/>
-      <c r="L1" s="5"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" ht="8.1" customHeight="1">
-      <c r="A2" s="6"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="11"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="50.25" customHeight="1">
-      <c r="A3" s="12"/>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="13"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="4" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A4" s="6"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="13"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12" ht="17.45" customHeight="1">
-      <c r="A5" s="6"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="14" t="s">
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="13"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12" ht="17.45" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="14" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="14" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="13"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A7" s="6"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="13"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A8" s="6"/>
+      <c r="A8" s="5"/>
       <c r="B8" s="36" t="s">
         <v>8</v>
       </c>
@@ -2043,10 +2043,10 @@
       <c r="I8" s="37"/>
       <c r="J8" s="37"/>
       <c r="K8" s="38"/>
-      <c r="L8" s="13"/>
+      <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A9" s="6"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="39" t="s">
         <v>9</v>
       </c>
@@ -2059,83 +2059,83 @@
       <c r="I9" s="40"/>
       <c r="J9" s="40"/>
       <c r="K9" s="41"/>
-      <c r="L9" s="13"/>
+      <c r="L9" s="12"/>
     </row>
     <row r="10" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="13"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="12"/>
     </row>
     <row r="11" spans="1:12" ht="15.6" customHeight="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="21" t="s">
+      <c r="K11" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="22"/>
+      <c r="L11" s="21"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1">
-      <c r="A12" s="19"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="22"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1">
-      <c r="A13" s="24"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="26"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="5">
